--- a/public/actius.xlsx
+++ b/public/actius.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7570CB0B-556E-4789-86F7-ABA22AE70FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -132,7 +132,7 @@
     <numFmt numFmtId="165" formatCode="#,##0\ _€"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0_ ;\-0.0\ "/>
-    <numFmt numFmtId="170" formatCode="\+0.00;\-0.00"/>
+    <numFmt numFmtId="168" formatCode="\+0.00;\-0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -331,10 +331,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,7 +809,7 @@
         <v>23.49520810509782</v>
       </c>
       <c r="C2" s="23">
-        <f>((100+D2)*(I2/100+1))*(H2/100+1)*(G2/100+1)*(F2/100+1)*(E2/100+1)</f>
+        <f t="shared" ref="C2:C21" si="0">((100+D2)*(I2/100+1))*(H2/100+1)*(G2/100+1)*(F2/100+1)*(E2/100+1)</f>
         <v>287.24371275599998</v>
       </c>
       <c r="D2" s="24"/>
@@ -845,7 +845,7 @@
         <v>273</v>
       </c>
       <c r="Q2" s="10">
-        <f t="shared" ref="Q2:Q10" si="0">(((O2/P2)^(1/25))-1)*100</f>
+        <f t="shared" ref="Q2:Q10" si="1">(((O2/P2)^(1/25))-1)*100</f>
         <v>10.091495639300829</v>
       </c>
     </row>
@@ -854,11 +854,11 @@
         <v>20</v>
       </c>
       <c r="B3" s="26">
-        <f t="shared" ref="B3:B21" si="1">(((C3/100)^(1/5))-1)*100</f>
+        <f t="shared" ref="B3:B21" si="2">(((C3/100)^(1/5))-1)*100</f>
         <v>14.483578637316018</v>
       </c>
       <c r="C3" s="23">
-        <f>((100+D3)*(I3/100+1))*(H3/100+1)*(G3/100+1)*(F3/100+1)*(E3/100+1)</f>
+        <f t="shared" si="0"/>
         <v>196.6599764336093</v>
       </c>
       <c r="D3" s="24">
@@ -896,7 +896,7 @@
         <v>1825</v>
       </c>
       <c r="Q3" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.5187110757897413</v>
       </c>
     </row>
@@ -905,11 +905,11 @@
         <v>25</v>
       </c>
       <c r="B4" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.51272107614041</v>
       </c>
       <c r="C4" s="23">
-        <f>((100+D4)*(I4/100+1))*(H4/100+1)*(G4/100+1)*(F4/100+1)*(E4/100+1)</f>
+        <f t="shared" si="0"/>
         <v>188.46151264329117</v>
       </c>
       <c r="D4" s="24">
@@ -947,7 +947,7 @@
         <v>11153</v>
       </c>
       <c r="Q4" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.0227688270235955</v>
       </c>
     </row>
@@ -956,11 +956,11 @@
         <v>5</v>
       </c>
       <c r="B5" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.8146962966187061</v>
       </c>
       <c r="C5" s="23">
-        <f>((100+D5)*(I5/100+1))*(H5/100+1)*(G5/100+1)*(F5/100+1)*(E5/100+1)</f>
+        <f t="shared" si="0"/>
         <v>145.6766075825937</v>
       </c>
       <c r="D5" s="24"/>
@@ -996,7 +996,7 @@
         <v>16095</v>
       </c>
       <c r="Q5" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.4720160546570371</v>
       </c>
     </row>
@@ -1005,11 +1005,11 @@
         <v>6</v>
       </c>
       <c r="B6" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.6985600166572077</v>
       </c>
       <c r="C6" s="23">
-        <f>((100+D6)*(I6/100+1))*(H6/100+1)*(G6/100+1)*(F6/100+1)*(E6/100+1)</f>
+        <f t="shared" si="0"/>
         <v>144.893693435953</v>
       </c>
       <c r="D6" s="24">
@@ -1047,7 +1047,7 @@
         <v>3045</v>
       </c>
       <c r="Q6" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7125520345924885</v>
       </c>
     </row>
@@ -1056,11 +1056,11 @@
         <v>0</v>
       </c>
       <c r="B7" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4358657323152055</v>
       </c>
       <c r="C7" s="23">
-        <f>((100+D7)*(I7/100+1))*(H7/100+1)*(G7/100+1)*(F7/100+1)*(E7/100+1)</f>
+        <f t="shared" si="0"/>
         <v>143.13519661776328</v>
       </c>
       <c r="D7" s="24"/>
@@ -1096,7 +1096,7 @@
         <v>24</v>
       </c>
       <c r="Q7" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.4924351144087549</v>
       </c>
     </row>
@@ -1105,11 +1105,11 @@
         <v>3</v>
       </c>
       <c r="B8" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4188593945777592</v>
       </c>
       <c r="C8" s="23">
-        <f>((100+D8)*(I8/100+1))*(H8/100+1)*(G8/100+1)*(F8/100+1)*(E8/100+1)</f>
+        <f t="shared" si="0"/>
         <v>143.02194603025421</v>
       </c>
       <c r="D8" s="24">
@@ -1147,7 +1147,7 @@
         <v>974</v>
       </c>
       <c r="Q8" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4442433057896515</v>
       </c>
     </row>
@@ -1156,11 +1156,11 @@
         <v>21</v>
       </c>
       <c r="B9" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.2732738190707247</v>
       </c>
       <c r="C9" s="23">
-        <f>((100+D9)*(I9/100+1))*(H9/100+1)*(G9/100+1)*(F9/100+1)*(E9/100+1)</f>
+        <f t="shared" si="0"/>
         <v>142.05537607019619</v>
       </c>
       <c r="D9" s="24"/>
@@ -1196,7 +1196,7 @@
         <v>247</v>
       </c>
       <c r="Q9" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.3135987794261634</v>
       </c>
     </row>
@@ -1205,11 +1205,11 @@
         <v>4</v>
       </c>
       <c r="B10" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.1415765899386363</v>
       </c>
       <c r="C10" s="23">
-        <f>((100+D10)*(I10/100+1))*(H10/100+1)*(G10/100+1)*(F10/100+1)*(E10/100+1)</f>
+        <f t="shared" si="0"/>
         <v>141.18552193481051</v>
       </c>
       <c r="D10" s="24">
@@ -1247,7 +1247,7 @@
         <v>918</v>
       </c>
       <c r="Q10" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.5425569365427494</v>
       </c>
     </row>
@@ -1256,11 +1256,11 @@
         <v>24</v>
       </c>
       <c r="B11" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.2425316712793277</v>
       </c>
       <c r="C11" s="23">
-        <f>((100+D11)*(I11/100+1))*(H11/100+1)*(G11/100+1)*(F11/100+1)*(E11/100+1)</f>
+        <f t="shared" si="0"/>
         <v>135.36053279109566</v>
       </c>
       <c r="D11" s="24">
@@ -1294,11 +1294,11 @@
         <v>9</v>
       </c>
       <c r="B12" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.4872902283462865</v>
       </c>
       <c r="C12" s="23">
-        <f>((100+D12)*(I12/100+1))*(H12/100+1)*(G12/100+1)*(F12/100+1)*(E12/100+1)</f>
+        <f t="shared" si="0"/>
         <v>130.61729371500533</v>
       </c>
       <c r="D12" s="24"/>
@@ -1330,11 +1330,11 @@
         <v>10</v>
       </c>
       <c r="B13" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.4199395835173414</v>
       </c>
       <c r="C13" s="23">
-        <f>((100+D13)*(I13/100+1))*(H13/100+1)*(G13/100+1)*(F13/100+1)*(E13/100+1)</f>
+        <f t="shared" si="0"/>
         <v>130.20084863260831</v>
       </c>
       <c r="D13" s="24"/>
@@ -1369,11 +1369,11 @@
         <v>15</v>
       </c>
       <c r="B14" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.5750736418072915</v>
       </c>
       <c r="C14" s="23">
-        <f>((100+D14)*(I14/100+1))*(H14/100+1)*(G14/100+1)*(F14/100+1)*(E14/100+1)</f>
+        <f t="shared" si="0"/>
         <v>119.19999955080596</v>
       </c>
       <c r="D14" s="24"/>
@@ -1408,11 +1408,11 @@
         <v>19</v>
       </c>
       <c r="B15" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.8603324315505496</v>
       </c>
       <c r="C15" s="23">
-        <f>((100+D15)*(I15/100+1))*(H15/100+1)*(G15/100+1)*(F15/100+1)*(E15/100+1)</f>
+        <f t="shared" si="0"/>
         <v>115.14355073353377</v>
       </c>
       <c r="D15" s="24">
@@ -1446,11 +1446,11 @@
         <v>23</v>
       </c>
       <c r="B16" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.7477866339479906</v>
       </c>
       <c r="C16" s="23">
-        <f>((100+D16)*(I16/100+1))*(H16/100+1)*(G16/100+1)*(F16/100+1)*(E16/100+1)</f>
+        <f t="shared" si="0"/>
         <v>114.51499961193853</v>
       </c>
       <c r="D16" s="24">
@@ -1484,11 +1484,11 @@
         <v>18</v>
       </c>
       <c r="B17" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8213577330986164</v>
       </c>
       <c r="C17" s="23">
-        <f>((100+D17)*(I17/100+1))*(H17/100+1)*(G17/100+1)*(F17/100+1)*(E17/100+1)</f>
+        <f t="shared" si="0"/>
         <v>109.44462035910999</v>
       </c>
       <c r="D17" s="24">
@@ -1522,11 +1522,11 @@
         <v>2</v>
       </c>
       <c r="B18" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7078007777595827</v>
       </c>
       <c r="C18" s="23">
-        <f>((100+D18)*(I18/100+1))*(H18/100+1)*(G18/100+1)*(F18/100+1)*(E18/100+1)</f>
+        <f t="shared" si="0"/>
         <v>108.83568585958317</v>
       </c>
       <c r="D18" s="24">
@@ -1561,11 +1561,11 @@
         <v>22</v>
       </c>
       <c r="B19" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.2432318635291484</v>
       </c>
       <c r="C19" s="23">
-        <f>((100+D19)*(I19/100+1))*(H19/100+1)*(G19/100+1)*(F19/100+1)*(E19/100+1)</f>
+        <f t="shared" si="0"/>
         <v>93.936493573264784</v>
       </c>
       <c r="D19" s="24"/>
@@ -1597,11 +1597,11 @@
         <v>1</v>
       </c>
       <c r="B20" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.270820560801289</v>
       </c>
       <c r="C20" s="23">
-        <f>((100+D20)*(I20/100+1))*(H20/100+1)*(G20/100+1)*(F20/100+1)*(E20/100+1)</f>
+        <f t="shared" si="0"/>
         <v>93.805356337491489</v>
       </c>
       <c r="D20" s="24"/>
@@ -1633,11 +1633,11 @@
         <v>26</v>
       </c>
       <c r="B21" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.4270850242224076</v>
       </c>
       <c r="C21" s="23">
-        <f>((100+D21)*(I21/100+1))*(H21/100+1)*(G21/100+1)*(F21/100+1)*(E21/100+1)</f>
+        <f t="shared" si="0"/>
         <v>93.065346363528775</v>
       </c>
       <c r="D21" s="24"/>
